--- a/0.说明文件与教程/药剂v2公式_工具草案.xlsx
+++ b/0.说明文件与教程/药剂v2公式_工具草案.xlsx
@@ -605,13 +605,13 @@
         <v>0</v>
       </c>
       <c r="O6">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V6">
         <v>1800</v>
@@ -646,7 +646,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D7" t="str">
         <v>meal</v>
@@ -682,13 +682,13 @@
         <v>0</v>
       </c>
       <c r="O7">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -700,7 +700,7 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V7">
         <v>1800</v>
@@ -723,7 +723,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C8">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D8" t="str">
         <v>meal</v>
@@ -759,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="O8">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -777,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V8">
         <v>1800</v>
@@ -800,7 +800,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D9" t="str">
         <v>meal</v>
@@ -836,13 +836,13 @@
         <v>0</v>
       </c>
       <c r="O9">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P9">
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -854,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V9">
         <v>1800</v>
@@ -877,7 +877,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C10">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D10" t="str">
         <v>meal</v>
@@ -913,13 +913,13 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="P10">
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -931,7 +931,7 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="V10">
         <v>1800</v>
@@ -990,13 +990,13 @@
         <v>0</v>
       </c>
       <c r="O11">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="P11">
         <v>0</v>
       </c>
       <c r="Q11">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -1008,7 +1008,7 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V11">
         <v>1800</v>
@@ -1031,7 +1031,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D12" t="str">
         <v>meal</v>
@@ -1067,13 +1067,13 @@
         <v>0</v>
       </c>
       <c r="O12">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="P12">
         <v>0</v>
       </c>
       <c r="Q12">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V12">
         <v>1800</v>
@@ -1108,7 +1108,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C13">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D13" t="str">
         <v>meal</v>
@@ -1144,13 +1144,13 @@
         <v>0</v>
       </c>
       <c r="O13">
-        <v>-12</v>
+        <v>-29</v>
       </c>
       <c r="P13">
         <v>0</v>
       </c>
       <c r="Q13">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="V13">
         <v>1800</v>
@@ -1185,7 +1185,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D14" t="str">
         <v>meal</v>
@@ -1221,13 +1221,13 @@
         <v>0</v>
       </c>
       <c r="O14">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P14">
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V14">
         <v>1800</v>
@@ -1262,7 +1262,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D15" t="str">
         <v>meal</v>
@@ -1298,13 +1298,13 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P15">
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V15">
         <v>1800</v>
@@ -1339,7 +1339,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C16">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D16" t="str">
         <v>meal</v>
@@ -1375,13 +1375,13 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="P16">
         <v>0</v>
       </c>
       <c r="Q16">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="R16">
         <v>0</v>
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="U16">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="V16">
         <v>1800</v>
@@ -1416,7 +1416,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C17">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="D17" t="str">
         <v>meal</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="O17">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -1470,7 +1470,7 @@
         <v>0</v>
       </c>
       <c r="U17">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="V17">
         <v>1800</v>
@@ -1493,7 +1493,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C18">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D18" t="str">
         <v>meal</v>
@@ -1529,13 +1529,13 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P18">
         <v>0</v>
       </c>
       <c r="Q18">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -1547,7 +1547,7 @@
         <v>0</v>
       </c>
       <c r="U18">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V18">
         <v>1800</v>
@@ -1570,7 +1570,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C19">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D19" t="str">
         <v>meal</v>
@@ -1606,7 +1606,7 @@
         <v>0</v>
       </c>
       <c r="O19">
-        <v>-12</v>
+        <v>-23</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -1624,7 +1624,7 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="V19">
         <v>1800</v>
@@ -1647,7 +1647,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C20">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D20" t="str">
         <v>meal</v>
@@ -1683,13 +1683,13 @@
         <v>0</v>
       </c>
       <c r="O20">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="P20">
         <v>0</v>
       </c>
       <c r="Q20">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -1701,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V20">
         <v>1800</v>
@@ -1724,7 +1724,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C21">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D21" t="str">
         <v>meal</v>
@@ -1760,13 +1760,13 @@
         <v>0</v>
       </c>
       <c r="O21">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="P21">
         <v>0</v>
       </c>
       <c r="Q21">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V21">
         <v>1800</v>
@@ -1801,7 +1801,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C22">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D22" t="str">
         <v>meal</v>
@@ -1837,13 +1837,13 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P22">
         <v>0</v>
       </c>
       <c r="Q22">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -1855,7 +1855,7 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V22">
         <v>1800</v>
@@ -1878,7 +1878,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C23">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D23" t="str">
         <v>meal</v>
@@ -1914,13 +1914,13 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P23">
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -1932,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V23">
         <v>1800</v>
@@ -1955,7 +1955,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C24">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D24" t="str">
         <v>meal</v>
@@ -1991,13 +1991,13 @@
         <v>0</v>
       </c>
       <c r="O24">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P24">
         <v>0</v>
       </c>
       <c r="Q24">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -2009,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="U24">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V24">
         <v>1800</v>
@@ -2068,13 +2068,13 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="P25">
         <v>0</v>
       </c>
       <c r="Q25">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -2086,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V25">
         <v>1800</v>
@@ -2109,7 +2109,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C26">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D26" t="str">
         <v>meal</v>
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="O26">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P26">
         <v>0</v>
       </c>
       <c r="Q26">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -2163,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="U26">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V26">
         <v>1800</v>
@@ -2186,7 +2186,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C27">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D27" t="str">
         <v>meal</v>
@@ -2222,13 +2222,13 @@
         <v>0</v>
       </c>
       <c r="O27">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P27">
         <v>0</v>
       </c>
       <c r="Q27">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -2240,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="U27">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V27">
         <v>1800</v>
@@ -2263,7 +2263,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C28">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D28" t="str">
         <v>meal</v>
@@ -2299,13 +2299,13 @@
         <v>0</v>
       </c>
       <c r="O28">
-        <v>-10</v>
+        <v>-23</v>
       </c>
       <c r="P28">
         <v>0</v>
       </c>
       <c r="Q28">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="U28">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="V28">
         <v>1800</v>
@@ -2340,7 +2340,7 @@
         <v>消耗品_酒水.xml</v>
       </c>
       <c r="C29">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D29" t="str">
         <v>meal</v>
@@ -2376,13 +2376,13 @@
         <v>0</v>
       </c>
       <c r="O29">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="P29">
         <v>0</v>
       </c>
       <c r="Q29">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="V29">
         <v>1800</v>
@@ -2453,13 +2453,13 @@
         <v>0</v>
       </c>
       <c r="O30">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="P30">
         <v>0</v>
       </c>
       <c r="Q30">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -2471,7 +2471,7 @@
         <v>0</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="V30">
         <v>1800</v>
